--- a/data/trans_orig/P1202-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1202-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener mucha energía en 2007</t>
+          <t>Población según la frecuencia de tener mucha energía en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>18514</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40333</t>
+          <t>39060</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42887</t>
+          <t>42426</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73366</t>
+          <t>71761</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66589</t>
+          <t>66770</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103558</t>
+          <t>102012</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61763</t>
+          <t>60977</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93717</t>
+          <t>94342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103922</t>
+          <t>105704</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>148343</t>
+          <t>150454</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>175804</t>
+          <t>177233</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>229018</t>
+          <t>230959</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>213335</t>
+          <t>213416</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>269909</t>
+          <t>270696</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>386172</t>
+          <t>390142</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>455618</t>
+          <t>456648</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>622246</t>
+          <t>619106</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>707455</t>
+          <t>704244</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>143339</t>
+          <t>145755</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>192700</t>
+          <t>192161</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>188524</t>
+          <t>189056</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>242216</t>
+          <t>241848</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>351263</t>
+          <t>350859</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>423983</t>
+          <t>418686</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>265685</t>
+          <t>265460</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>321454</t>
+          <t>322797</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>286450</t>
+          <t>283018</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>345957</t>
+          <t>346513</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>563845</t>
+          <t>567986</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>646419</t>
+          <t>650441</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,72%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>201110</t>
+          <t>198743</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>254684</t>
+          <t>252065</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>158674</t>
+          <t>161469</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>209463</t>
+          <t>209054</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>370094</t>
+          <t>371660</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>448331</t>
+          <t>447609</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11734</t>
+          <t>11606</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28726</t>
+          <t>29375</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14536</t>
+          <t>14234</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33082</t>
+          <t>33810</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30504</t>
+          <t>30674</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57611</t>
+          <t>57365</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1618,7 +1618,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38287</t>
+          <t>37187</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>66151</t>
+          <t>65220</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52666</t>
+          <t>53623</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85639</t>
+          <t>86628</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>101361</t>
+          <t>100289</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>146165</t>
+          <t>143634</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160791</t>
+          <t>161960</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>211538</t>
+          <t>212611</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>241828</t>
+          <t>238885</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>302854</t>
+          <t>298690</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>417685</t>
+          <t>415737</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>495876</t>
+          <t>493692</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>237359</t>
+          <t>234669</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>298879</t>
+          <t>297650</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>305725</t>
+          <t>305550</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>371136</t>
+          <t>372270</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>558670</t>
+          <t>554139</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>646088</t>
+          <t>642088</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>604195</t>
+          <t>605823</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>681606</t>
+          <t>683981</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,68%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>537235</t>
+          <t>534094</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>611755</t>
+          <t>607991</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1157391</t>
+          <t>1158219</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1267885</t>
+          <t>1269762</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,7%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>491178</t>
+          <t>490595</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>566921</t>
+          <t>567433</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>28,97%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>288351</t>
+          <t>284571</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>349086</t>
+          <t>351345</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>800275</t>
+          <t>801950</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>895908</t>
+          <t>902952</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2178,12 +2178,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,52%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>256</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11247</t>
+          <t>11373</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11875</t>
+          <t>11274</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17762</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10611</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27749</t>
+          <t>27546</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15892</t>
+          <t>15962</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36191</t>
+          <t>36891</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29781</t>
+          <t>30495</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55451</t>
+          <t>55349</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52107</t>
+          <t>52576</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>83003</t>
+          <t>82864</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76732</t>
+          <t>76451</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>111337</t>
+          <t>112191</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>138691</t>
+          <t>137616</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>185114</t>
+          <t>185352</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>54743</t>
+          <t>55403</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>88245</t>
+          <t>89606</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64050</t>
+          <t>64985</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>96935</t>
+          <t>99417</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>128069</t>
+          <t>126159</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>174002</t>
+          <t>172852</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>186036</t>
+          <t>185767</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>231377</t>
+          <t>234937</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>165649</t>
+          <t>165528</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>208863</t>
+          <t>206789</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>363063</t>
+          <t>361091</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>424980</t>
+          <t>426080</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,45%</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>161593</t>
+          <t>161334</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>207703</t>
+          <t>206728</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,67%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>72863</t>
+          <t>71478</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>105993</t>
+          <t>106432</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>244094</t>
+          <t>245000</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>301603</t>
+          <t>302405</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37432</t>
+          <t>37402</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>66062</t>
+          <t>64160</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>64945</t>
+          <t>64100</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>100501</t>
+          <t>100382</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>110514</t>
+          <t>113042</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>157020</t>
+          <t>157616</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>120964</t>
+          <t>121698</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>169654</t>
+          <t>168974</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>189345</t>
+          <t>190765</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>248154</t>
+          <t>248258</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>321715</t>
+          <t>325449</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>400250</t>
+          <t>398201</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>456072</t>
+          <t>457411</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>542208</t>
+          <t>542295</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>733846</t>
+          <t>736052</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>834905</t>
+          <t>836834</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>24,71%</t>
+          <t>24,76%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1210515</t>
+          <t>1217529</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1337546</t>
+          <t>1342979</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>462970</t>
+          <t>467935</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>548434</t>
+          <t>548547</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>591167</t>
+          <t>587259</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>683344</t>
+          <t>678306</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1068463</t>
+          <t>1077516</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1196161</t>
+          <t>1199669</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1092227</t>
+          <t>1095200</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1201950</t>
+          <t>1201043</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>33,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1015047</t>
+          <t>1020138</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1125265</t>
+          <t>1128150</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,47 +3620,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,04%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>33,39%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>2190</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2216317</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2142748</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>2297843</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>33,3%</t>
         </is>
       </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2190</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>2216317</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>2141312</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>2301815</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>33,3%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,52%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>882192</t>
+          <t>882656</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>993790</t>
+          <t>988777</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>555116</t>
+          <t>545922</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>638824</t>
+          <t>634257</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1463247</t>
+          <t>1460246</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1604042</t>
+          <t>1600788</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3949,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener mucha energía en 2012</t>
+          <t>Población según la frecuencia de tener mucha energía en 2012 (tasa de respuesta: 99,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19734</t>
+          <t>19673</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43758</t>
+          <t>44407</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>75070</t>
+          <t>74772</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>112898</t>
+          <t>113430</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101932</t>
+          <t>101113</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>148227</t>
+          <t>147118</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,37%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>51989</t>
+          <t>52217</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86618</t>
+          <t>86580</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86602</t>
+          <t>87861</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>127554</t>
+          <t>128392</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>147184</t>
+          <t>148246</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200702</t>
+          <t>199870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>175246</t>
+          <t>176756</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>227573</t>
+          <t>226311</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>337494</t>
+          <t>338030</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>403709</t>
+          <t>405591</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,25%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>527921</t>
+          <t>527183</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>614271</t>
+          <t>616850</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>104227</t>
+          <t>106678</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>147491</t>
+          <t>149881</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>169575</t>
+          <t>168858</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>221820</t>
+          <t>221551</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>286071</t>
+          <t>287972</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>352819</t>
+          <t>354388</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,34%</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>262658</t>
+          <t>259816</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>320397</t>
+          <t>322322</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>308767</t>
+          <t>308884</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>376193</t>
+          <t>373720</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>588557</t>
+          <t>590703</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>675426</t>
+          <t>679508</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>233400</t>
+          <t>233743</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>291085</t>
+          <t>288716</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>29,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>206041</t>
+          <t>207327</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>267386</t>
+          <t>264148</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>449521</t>
+          <t>454795</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>531708</t>
+          <t>532474</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,05%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30294</t>
+          <t>30716</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>56856</t>
+          <t>57205</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46972</t>
+          <t>48361</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83458</t>
+          <t>83430</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88064</t>
+          <t>87731</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>132022</t>
+          <t>131532</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26061</t>
+          <t>25914</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52830</t>
+          <t>51117</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65891</t>
+          <t>65314</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>103337</t>
+          <t>102642</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>96416</t>
+          <t>96910</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>144279</t>
+          <t>141134</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>193000</t>
+          <t>193741</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>249673</t>
+          <t>250318</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>237267</t>
+          <t>235371</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>298391</t>
+          <t>300519</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>448378</t>
+          <t>447728</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>524302</t>
+          <t>529012</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,24%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>248899</t>
+          <t>249309</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311683</t>
+          <t>311731</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5293,7 +5293,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>227053</t>
+          <t>225464</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>286329</t>
+          <t>284578</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>486259</t>
+          <t>489708</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>575294</t>
+          <t>578405</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>565270</t>
+          <t>565176</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>651893</t>
+          <t>647990</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>516352</t>
+          <t>513343</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>598532</t>
+          <t>596835</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1111336</t>
+          <t>1097177</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1225984</t>
+          <t>1216126</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,53%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>733770</t>
+          <t>731519</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>820416</t>
+          <t>818918</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>492410</t>
+          <t>488826</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>571262</t>
+          <t>569268</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1244035</t>
+          <t>1250692</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1367561</t>
+          <t>1363010</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,68%</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>1968</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11323</t>
+          <t>11905</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3117</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14885</t>
+          <t>14254</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6027</t>
+          <t>6108</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20417</t>
+          <t>20154</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2332</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18215</t>
+          <t>17338</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6849</t>
+          <t>6917</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21627</t>
+          <t>22693</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32834</t>
+          <t>33279</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42079</t>
+          <t>44305</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>73493</t>
+          <t>77421</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50066</t>
+          <t>51331</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>82892</t>
+          <t>81874</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>100432</t>
+          <t>101012</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>144135</t>
+          <t>145233</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>59160</t>
+          <t>60067</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>96843</t>
+          <t>95114</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>52908</t>
+          <t>51390</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>84062</t>
+          <t>85101</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>121026</t>
+          <t>120801</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>169905</t>
+          <t>169668</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,09%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133659</t>
+          <t>133721</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>177622</t>
+          <t>178320</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,99%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>131527</t>
+          <t>132690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>175357</t>
+          <t>175466</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>280728</t>
+          <t>280479</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>339978</t>
+          <t>346187</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>36,91%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>156723</t>
+          <t>157880</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>200378</t>
+          <t>205295</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>130787</t>
+          <t>130196</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>173890</t>
+          <t>174267</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>302593</t>
+          <t>298873</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>361716</t>
+          <t>361003</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,49%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>60781</t>
+          <t>59969</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>96408</t>
+          <t>97897</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>140358</t>
+          <t>140273</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>192197</t>
+          <t>193250</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>211049</t>
+          <t>210228</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>274926</t>
+          <t>271762</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>90580</t>
+          <t>90372</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>136011</t>
+          <t>135516</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>174497</t>
+          <t>176581</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>233625</t>
+          <t>234759</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>279123</t>
+          <t>278815</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>353542</t>
+          <t>351386</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>439954</t>
+          <t>437453</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>522220</t>
+          <t>523276</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>648401</t>
+          <t>651200</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>748906</t>
+          <t>749987</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1119788</t>
+          <t>1117944</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1248384</t>
+          <t>1245581</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,89%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>442023</t>
+          <t>440318</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>523397</t>
+          <t>521942</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>470564</t>
+          <t>473504</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>556931</t>
+          <t>560422</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>935137</t>
+          <t>938060</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1056624</t>
+          <t>1055432</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,16%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>995771</t>
+          <t>997956</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1113880</t>
+          <t>1113813</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6996,7 +6996,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>996862</t>
+          <t>992411</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1108281</t>
+          <t>1108661</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2022436</t>
+          <t>2022168</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2188261</t>
+          <t>2182922</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,35%</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1157623</t>
+          <t>1155998</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1272460</t>
+          <t>1278070</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>859571</t>
+          <t>863533</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>968608</t>
+          <t>973811</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2047526</t>
+          <t>2056987</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2207672</t>
+          <t>2218471</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,86%</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7360,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener mucha energía en 2016</t>
+          <t>Población según la frecuencia de tener mucha energía en 2016 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18157</t>
+          <t>18250</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36807</t>
+          <t>37566</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45860</t>
+          <t>45621</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77077</t>
+          <t>76490</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>69751</t>
+          <t>68434</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>105900</t>
+          <t>106289</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34481</t>
+          <t>35545</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60979</t>
+          <t>63119</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105119</t>
+          <t>100964</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>149018</t>
+          <t>146884</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>144871</t>
+          <t>148276</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>199010</t>
+          <t>199332</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -7781,12 +7781,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>146661</t>
+          <t>147412</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>191812</t>
+          <t>192449</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>225782</t>
+          <t>225561</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>285385</t>
+          <t>284737</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>387485</t>
+          <t>388414</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>462621</t>
+          <t>459482</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>159524</t>
+          <t>160405</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>207170</t>
+          <t>206722</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>195881</t>
+          <t>194912</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>252032</t>
+          <t>249809</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>369687</t>
+          <t>369955</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>444678</t>
+          <t>441240</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>129777</t>
+          <t>129092</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>173122</t>
+          <t>174027</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>149856</t>
+          <t>151786</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>199070</t>
+          <t>201196</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>296155</t>
+          <t>291298</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>358906</t>
+          <t>359793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8092,12 +8092,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8120,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>153339</t>
+          <t>154266</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>201070</t>
+          <t>202555</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>130514</t>
+          <t>132468</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>180092</t>
+          <t>179856</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>297227</t>
+          <t>296667</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>365135</t>
+          <t>363539</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -8350,12 +8350,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15742</t>
+          <t>16014</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37246</t>
+          <t>38137</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>29962</t>
+          <t>30719</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56672</t>
+          <t>56667</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52345</t>
+          <t>50629</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87151</t>
+          <t>84580</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -8463,12 +8463,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>36505</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>66328</t>
+          <t>65280</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59101</t>
+          <t>58423</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>93980</t>
+          <t>94454</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>103779</t>
+          <t>105027</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>150882</t>
+          <t>148284</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -8576,12 +8576,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>169788</t>
+          <t>172113</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>223958</t>
+          <t>223010</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>220893</t>
+          <t>224253</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>283244</t>
+          <t>285642</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>408015</t>
+          <t>411662</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>491156</t>
+          <t>494681</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>348696</t>
+          <t>345064</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>419063</t>
+          <t>418767</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>325577</t>
+          <t>325853</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>394345</t>
+          <t>398078</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>694209</t>
+          <t>693852</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>795771</t>
+          <t>794143</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8779,7 +8779,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>589838</t>
+          <t>585633</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>673603</t>
+          <t>671138</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>32,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>548043</t>
+          <t>548261</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>627422</t>
+          <t>630274</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8852,12 +8852,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1156452</t>
+          <t>1150470</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1279349</t>
+          <t>1273052</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8887,12 +8887,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,35%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,37%</t>
         </is>
       </c>
     </row>
@@ -8915,12 +8915,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>747101</t>
+          <t>744342</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>836973</t>
+          <t>833169</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>624128</t>
+          <t>622378</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>708831</t>
+          <t>704826</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1395387</t>
+          <t>1395742</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1520566</t>
+          <t>1517653</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9000,12 +9000,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -9145,12 +9145,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16776</t>
+          <t>17246</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9160,77 +9160,77 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>5780</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2068</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>13498</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>14623</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>7755</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>25090</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>5780</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1839</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>13435</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>2,45%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>14623</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>8036</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>25026</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -9258,12 +9258,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3118</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14683</t>
+          <t>14752</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5642</t>
+          <t>5171</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21376</t>
+          <t>21468</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9308,47 +9308,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>18316</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>11225</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>29022</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>1,67%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>1,03%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>18316</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>10564</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>30040</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>1,67%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>43958</t>
+          <t>42322</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>72675</t>
+          <t>71031</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>53912</t>
+          <t>54118</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86913</t>
+          <t>85074</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>105093</t>
+          <t>103154</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>149670</t>
+          <t>146133</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>89972</t>
+          <t>90140</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>127725</t>
+          <t>127775</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9499,7 +9499,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>94400</t>
+          <t>91315</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>134549</t>
+          <t>129100</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9534,12 +9534,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>192516</t>
+          <t>195748</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>246860</t>
+          <t>249908</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,55%</t>
+          <t>22,82%</t>
         </is>
       </c>
     </row>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>151398</t>
+          <t>150066</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>197363</t>
+          <t>193879</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>155672</t>
+          <t>155609</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>200001</t>
+          <t>200335</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>36,55%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>318965</t>
+          <t>316064</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>380456</t>
+          <t>383230</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>35,0%</t>
         </is>
       </c>
     </row>
@@ -9710,12 +9710,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>171939</t>
+          <t>170325</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>220625</t>
+          <t>218694</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9725,12 +9725,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>154844</t>
+          <t>154761</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>198767</t>
+          <t>199606</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>338654</t>
+          <t>338938</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>403027</t>
+          <t>403760</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -9940,12 +9940,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46715</t>
+          <t>45235</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>77891</t>
+          <t>78368</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>89368</t>
+          <t>89128</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>131341</t>
+          <t>130274</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>141072</t>
+          <t>141256</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>195082</t>
+          <t>196549</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>87179</t>
+          <t>85015</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>129920</t>
+          <t>125200</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>181836</t>
+          <t>179459</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>241738</t>
+          <t>239533</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10103,47 +10103,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>6,79%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>314809</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>283091</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>355876</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>4,1%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>5,16%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>314809</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>277617</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>351841</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10166,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>383412</t>
+          <t>382526</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>463015</t>
+          <t>458206</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>531006</t>
+          <t>532133</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>622545</t>
+          <t>628167</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10216,12 +10216,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>940054</t>
+          <t>940669</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1053564</t>
+          <t>1061209</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>629906</t>
+          <t>629647</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>719480</t>
+          <t>721101</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>641180</t>
+          <t>641993</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>741167</t>
+          <t>739274</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1301251</t>
+          <t>1298925</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1433166</t>
+          <t>1441250</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,89%</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>895109</t>
+          <t>904021</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1006067</t>
+          <t>1010910</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>887115</t>
+          <t>884871</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>993806</t>
+          <t>1000846</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10442,12 +10442,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1818008</t>
+          <t>1823733</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1978218</t>
+          <t>1971937</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,58%</t>
         </is>
       </c>
     </row>
@@ -10505,12 +10505,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1107554</t>
+          <t>1100986</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1218368</t>
+          <t>1217088</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10540,12 +10540,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>944486</t>
+          <t>939468</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1052329</t>
+          <t>1056858</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10575,12 +10575,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2077173</t>
+          <t>2075747</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2240058</t>
+          <t>2229062</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,31%</t>
         </is>
       </c>
     </row>
@@ -10771,7 +10771,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia de tener mucha energía en 2023</t>
+          <t>Población según la frecuencia de tener mucha energía en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10966,12 +10966,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>15077</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31479</t>
+          <t>30653</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10981,12 +10981,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54973</t>
+          <t>54157</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76422</t>
+          <t>75658</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75311</t>
+          <t>75555</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100645</t>
+          <t>101125</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -11079,12 +11079,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34906</t>
+          <t>35897</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>59668</t>
+          <t>58512</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11094,12 +11094,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>74108</t>
+          <t>73517</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>99031</t>
+          <t>98887</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11129,12 +11129,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>113886</t>
+          <t>115289</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148847</t>
+          <t>148490</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11164,12 +11164,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -11192,12 +11192,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>86032</t>
+          <t>87173</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>116736</t>
+          <t>117465</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11207,12 +11207,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>166762</t>
+          <t>164211</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>206530</t>
+          <t>203982</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11242,12 +11242,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11262,12 +11262,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>260026</t>
+          <t>259062</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>308936</t>
+          <t>308790</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11277,12 +11277,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,34%</t>
         </is>
       </c>
     </row>
@@ -11305,12 +11305,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88828</t>
+          <t>89123</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124850</t>
+          <t>124907</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>130104</t>
+          <t>131544</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>163537</t>
+          <t>164359</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11375,12 +11375,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>229655</t>
+          <t>229587</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>277868</t>
+          <t>278271</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11390,12 +11390,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>21,94%</t>
         </is>
       </c>
     </row>
@@ -11418,12 +11418,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97366</t>
+          <t>97657</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133736</t>
+          <t>132958</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11453,12 +11453,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>143020</t>
+          <t>143223</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>177495</t>
+          <t>177200</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11468,12 +11468,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11488,12 +11488,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>249869</t>
+          <t>250416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>298027</t>
+          <t>299757</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11503,12 +11503,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -11531,12 +11531,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>105414</t>
+          <t>105975</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>143212</t>
+          <t>141365</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11546,12 +11546,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11566,12 +11566,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>100060</t>
+          <t>98337</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>132655</t>
+          <t>131596</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11581,12 +11581,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11601,12 +11601,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>215844</t>
+          <t>215159</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>264806</t>
+          <t>263526</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11616,12 +11616,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -11761,12 +11761,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16503</t>
+          <t>15837</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>40224</t>
+          <t>37453</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23598</t>
+          <t>24651</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50398</t>
+          <t>52702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11811,12 +11811,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>46376</t>
+          <t>45971</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81082</t>
+          <t>81250</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11874,12 +11874,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45850</t>
+          <t>45806</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>87635</t>
+          <t>89103</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11909,12 +11909,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64209</t>
+          <t>67363</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>112003</t>
+          <t>113949</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11924,12 +11924,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11944,12 +11944,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>125160</t>
+          <t>128959</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>189069</t>
+          <t>191423</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11959,12 +11959,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -11987,12 +11987,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>155467</t>
+          <t>152543</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>262527</t>
+          <t>262701</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12022,12 +12022,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>218587</t>
+          <t>226274</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>349371</t>
+          <t>352816</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12037,12 +12037,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>428523</t>
+          <t>424182</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>594324</t>
+          <t>599843</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -12100,12 +12100,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315628</t>
+          <t>311600</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1087381</t>
+          <t>1101965</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12115,12 +12115,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12135,12 +12135,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>194245</t>
+          <t>205219</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>323047</t>
+          <t>321367</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12150,12 +12150,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12170,12 +12170,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>575604</t>
+          <t>574181</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1488754</t>
+          <t>1408238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12185,12 +12185,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -12213,12 +12213,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>408774</t>
+          <t>407725</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>664350</t>
+          <t>669578</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12228,12 +12228,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12248,12 +12248,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>618834</t>
+          <t>615116</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1222166</t>
+          <t>1162593</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12263,12 +12263,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12283,12 +12283,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1155063</t>
+          <t>1165198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1855304</t>
+          <t>1853362</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12298,12 +12298,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,94%</t>
         </is>
       </c>
     </row>
@@ -12326,12 +12326,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>573435</t>
+          <t>588695</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>979975</t>
+          <t>984543</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12341,12 +12341,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12361,12 +12361,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>520809</t>
+          <t>558305</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>833707</t>
+          <t>831355</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12396,12 +12396,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1279672</t>
+          <t>1271818</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1769804</t>
+          <t>1774196</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>39,19%</t>
         </is>
       </c>
     </row>
@@ -12556,12 +12556,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14360</t>
+          <t>14917</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12571,12 +12571,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12591,12 +12591,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2827</t>
+          <t>2542</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10760</t>
+          <t>10368</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12606,47 +12606,47 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>1,57%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>10564</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>5673</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>20430</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>0,43%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>10564</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>5719</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>19319</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,56%</t>
         </is>
       </c>
     </row>
@@ -12669,12 +12669,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19894</t>
+          <t>20214</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45017</t>
+          <t>44132</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12684,12 +12684,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12704,12 +12704,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12181</t>
+          <t>12096</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26324</t>
+          <t>26599</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12719,12 +12719,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12739,12 +12739,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36572</t>
+          <t>37572</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64130</t>
+          <t>64734</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -12782,12 +12782,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>59928</t>
+          <t>60199</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93136</t>
+          <t>93042</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12797,12 +12797,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12817,12 +12817,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90455</t>
+          <t>88714</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>122298</t>
+          <t>122042</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12832,12 +12832,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12852,12 +12852,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>158691</t>
+          <t>157491</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>206489</t>
+          <t>204395</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12867,12 +12867,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -12895,12 +12895,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77904</t>
+          <t>76385</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>112611</t>
+          <t>112593</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12910,12 +12910,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>96769</t>
+          <t>97408</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>130999</t>
+          <t>130072</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12945,12 +12945,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12965,12 +12965,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>183910</t>
+          <t>180874</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>230951</t>
+          <t>228785</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12980,12 +12980,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -13008,12 +13008,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>156093</t>
+          <t>159042</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>204419</t>
+          <t>207628</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13023,12 +13023,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13043,12 +13043,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>186208</t>
+          <t>185979</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>229631</t>
+          <t>226502</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13078,12 +13078,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>357349</t>
+          <t>357406</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>419427</t>
+          <t>420549</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,21%</t>
         </is>
       </c>
     </row>
@@ -13121,12 +13121,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>233414</t>
+          <t>236869</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>293061</t>
+          <t>291442</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13136,12 +13136,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>188256</t>
+          <t>190302</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>233583</t>
+          <t>234181</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13191,12 +13191,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>437072</t>
+          <t>438449</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>510459</t>
+          <t>511871</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,21%</t>
         </is>
       </c>
     </row>
@@ -13351,12 +13351,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40109</t>
+          <t>40479</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>70007</t>
+          <t>69383</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13386,12 +13386,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>83228</t>
+          <t>86775</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>123179</t>
+          <t>126384</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13401,12 +13401,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13421,12 +13421,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>132398</t>
+          <t>132946</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>184457</t>
+          <t>184782</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -13464,12 +13464,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>112691</t>
+          <t>109052</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>172648</t>
+          <t>171459</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13479,12 +13479,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13499,12 +13499,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>155013</t>
+          <t>157640</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>218845</t>
+          <t>222773</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13514,12 +13514,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13534,12 +13534,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>297111</t>
+          <t>291438</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>377672</t>
+          <t>379865</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13549,12 +13549,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>314008</t>
+          <t>309483</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>453079</t>
+          <t>449980</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13592,12 +13592,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13612,12 +13612,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>460789</t>
+          <t>471503</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>648293</t>
+          <t>649031</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13627,12 +13627,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13647,12 +13647,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>867446</t>
+          <t>848543</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1077926</t>
+          <t>1071427</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13662,12 +13662,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,09%</t>
         </is>
       </c>
     </row>
@@ -13690,12 +13690,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>514583</t>
+          <t>511137</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1326278</t>
+          <t>1327150</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13705,12 +13705,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13725,12 +13725,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>440903</t>
+          <t>443861</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>593815</t>
+          <t>590690</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13760,12 +13760,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1024823</t>
+          <t>1027232</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2004451</t>
+          <t>2025024</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,52%</t>
         </is>
       </c>
     </row>
@@ -13803,12 +13803,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>683459</t>
+          <t>701212</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>959299</t>
+          <t>964993</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13818,12 +13818,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>985029</t>
+          <t>981464</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1719155</t>
+          <t>1642775</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13873,12 +13873,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1808105</t>
+          <t>1814856</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2503635</t>
+          <t>2579478</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -13916,12 +13916,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>994145</t>
+          <t>956404</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1367508</t>
+          <t>1363972</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13931,12 +13931,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>27,71%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13951,12 +13951,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>846064</t>
+          <t>850195</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1147606</t>
+          <t>1147983</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13986,12 +13986,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2011276</t>
+          <t>2003700</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2469619</t>
+          <t>2467481</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>34,75%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1202-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1202-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18514</t>
+          <t>18812</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39060</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>42426</t>
+          <t>43522</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71761</t>
+          <t>73230</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66770</t>
+          <t>65585</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102012</t>
+          <t>101280</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>60977</t>
+          <t>61282</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94342</t>
+          <t>95616</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105704</t>
+          <t>105362</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>150454</t>
+          <t>146951</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>177233</t>
+          <t>174164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>230959</t>
+          <t>227775</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,71%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>213416</t>
+          <t>216479</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>270696</t>
+          <t>273062</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>390142</t>
+          <t>389703</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>456648</t>
+          <t>459184</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>619106</t>
+          <t>618912</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>704244</t>
+          <t>703872</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>29,99%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>145755</t>
+          <t>147218</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>192161</t>
+          <t>192287</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>189056</t>
+          <t>190434</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>241848</t>
+          <t>241888</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>350859</t>
+          <t>351494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>418686</t>
+          <t>422150</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>265460</t>
+          <t>263446</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>322797</t>
+          <t>324377</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>283018</t>
+          <t>284337</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>346513</t>
+          <t>348971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>567986</t>
+          <t>566312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>650441</t>
+          <t>649461</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,67%</t>
         </is>
       </c>
     </row>
@@ -1298,12 +1298,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>198743</t>
+          <t>199986</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>252065</t>
+          <t>253063</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1333,12 +1333,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>161469</t>
+          <t>160416</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>209054</t>
+          <t>206650</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1348,12 +1348,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>371660</t>
+          <t>373284</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>447609</t>
+          <t>446815</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1383,12 +1383,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11263</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29375</t>
+          <t>28622</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14234</t>
+          <t>14070</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33810</t>
+          <t>32884</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>30674</t>
+          <t>29311</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>57365</t>
+          <t>54826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>37187</t>
+          <t>38740</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65220</t>
+          <t>67002</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>53623</t>
+          <t>54433</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>86628</t>
+          <t>86024</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>100289</t>
+          <t>97571</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>143634</t>
+          <t>143112</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,36%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>161960</t>
+          <t>160793</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>212611</t>
+          <t>213987</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>238885</t>
+          <t>238287</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>298690</t>
+          <t>299853</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>415737</t>
+          <t>418362</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>493692</t>
+          <t>499120</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,21%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>234669</t>
+          <t>235722</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>297650</t>
+          <t>294776</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>305550</t>
+          <t>303410</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>372270</t>
+          <t>370578</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>554139</t>
+          <t>559947</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>642088</t>
+          <t>652520</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>605823</t>
+          <t>601115</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>683981</t>
+          <t>681833</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>534094</t>
+          <t>533051</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>607991</t>
+          <t>608063</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2030,12 +2030,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1158219</t>
+          <t>1156455</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1269762</t>
+          <t>1267280</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,62%</t>
         </is>
       </c>
     </row>
@@ -2093,12 +2093,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>490595</t>
+          <t>492039</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>567433</t>
+          <t>567462</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2108,7 +2108,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2128,12 +2128,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>284571</t>
+          <t>287777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>351345</t>
+          <t>354350</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2143,12 +2143,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>801950</t>
+          <t>801940</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>902952</t>
+          <t>902402</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>992</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11373</t>
+          <t>11892</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11274</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17762</t>
+          <t>16911</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10611</t>
+          <t>10484</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>27546</t>
+          <t>27212</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15962</t>
+          <t>14605</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36891</t>
+          <t>35244</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>30495</t>
+          <t>30088</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55349</t>
+          <t>56183</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,47%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>52576</t>
+          <t>51792</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82864</t>
+          <t>84105</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>76451</t>
+          <t>77611</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>112191</t>
+          <t>112007</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>137616</t>
+          <t>138627</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>185352</t>
+          <t>184110</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -2662,12 +2662,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>55403</t>
+          <t>55817</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>89606</t>
+          <t>87294</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64985</t>
+          <t>63484</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>99417</t>
+          <t>97776</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>126159</t>
+          <t>128520</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>172852</t>
+          <t>175367</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>17,06%</t>
         </is>
       </c>
     </row>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>185767</t>
+          <t>187676</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>234937</t>
+          <t>232961</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,12 +2810,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>165528</t>
+          <t>164389</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>206789</t>
+          <t>208557</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,12 +2845,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>361091</t>
+          <t>360712</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>426080</t>
+          <t>425804</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,13%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>41,43%</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>161334</t>
+          <t>162945</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>206728</t>
+          <t>208677</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2903,12 +2903,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,12 +2923,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>71478</t>
+          <t>71907</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>106432</t>
+          <t>105631</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2958,12 +2958,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>245000</t>
+          <t>241679</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>302405</t>
+          <t>301392</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,32%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>37402</t>
+          <t>38827</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>64160</t>
+          <t>66431</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>64100</t>
+          <t>66024</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>100382</t>
+          <t>101741</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>113042</t>
+          <t>111077</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>157616</t>
+          <t>156863</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>121698</t>
+          <t>123193</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>168974</t>
+          <t>170092</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>190765</t>
+          <t>189024</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>248258</t>
+          <t>248669</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>325449</t>
+          <t>327684</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>398201</t>
+          <t>402909</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>457411</t>
+          <t>453347</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>542295</t>
+          <t>533622</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>736052</t>
+          <t>735629</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>836834</t>
+          <t>831512</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1217529</t>
+          <t>1215423</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1342979</t>
+          <t>1345778</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,22%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>467935</t>
+          <t>463558</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>548547</t>
+          <t>544894</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>587259</t>
+          <t>591959</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>678306</t>
+          <t>683232</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1077516</t>
+          <t>1074838</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1199669</t>
+          <t>1200859</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1095200</t>
+          <t>1090549</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1201043</t>
+          <t>1198052</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1020138</t>
+          <t>1022758</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1128150</t>
+          <t>1125904</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>33,39%</t>
+          <t>33,32%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2142748</t>
+          <t>2137619</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2297843</t>
+          <t>2289057</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,39%</t>
         </is>
       </c>
     </row>
@@ -3683,12 +3683,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>882656</t>
+          <t>886442</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>988777</t>
+          <t>992170</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3698,12 +3698,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>545922</t>
+          <t>546741</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>634257</t>
+          <t>637543</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3733,12 +3733,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,12 +3753,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>1460246</t>
+          <t>1459750</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>1600788</t>
+          <t>1605062</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,12%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19673</t>
+          <t>18971</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44407</t>
+          <t>42498</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74772</t>
+          <t>74254</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113430</t>
+          <t>113262</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101113</t>
+          <t>101273</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147118</t>
+          <t>145933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,32%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52217</t>
+          <t>52072</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>86580</t>
+          <t>86901</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87861</t>
+          <t>88771</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>128392</t>
+          <t>129028</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>148246</t>
+          <t>146911</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>199870</t>
+          <t>196656</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>176756</t>
+          <t>176903</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>226311</t>
+          <t>231274</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>338030</t>
+          <t>335438</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>405591</t>
+          <t>401470</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>527183</t>
+          <t>529317</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>616850</t>
+          <t>616305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>106678</t>
+          <t>105414</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>149881</t>
+          <t>146402</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168858</t>
+          <t>168857</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>221551</t>
+          <t>221623</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>287972</t>
+          <t>288043</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>354388</t>
+          <t>357860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>259816</t>
+          <t>260897</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>322322</t>
+          <t>321916</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>308884</t>
+          <t>307047</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>373720</t>
+          <t>372817</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>590703</t>
+          <t>589143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>679508</t>
+          <t>677848</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -4709,12 +4709,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>233743</t>
+          <t>234840</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>288716</t>
+          <t>289074</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4724,12 +4724,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>207327</t>
+          <t>206940</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>264148</t>
+          <t>262078</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4759,12 +4759,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4779,12 +4779,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>454795</t>
+          <t>451083</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>532474</t>
+          <t>533375</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4794,12 +4794,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30716</t>
+          <t>31175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57205</t>
+          <t>58220</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48361</t>
+          <t>48914</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>83430</t>
+          <t>83384</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>87731</t>
+          <t>86911</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>131532</t>
+          <t>130844</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>25459</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51117</t>
+          <t>50286</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65314</t>
+          <t>65810</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>102642</t>
+          <t>103655</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>96910</t>
+          <t>97063</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>141134</t>
+          <t>142484</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>193741</t>
+          <t>195522</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>250318</t>
+          <t>254438</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>235371</t>
+          <t>235503</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>300519</t>
+          <t>300198</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>447728</t>
+          <t>447027</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>529012</t>
+          <t>531427</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>249309</t>
+          <t>246034</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311731</t>
+          <t>312941</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>225464</t>
+          <t>222807</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>284578</t>
+          <t>283714</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>489708</t>
+          <t>491904</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>578405</t>
+          <t>577670</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,55%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>565176</t>
+          <t>563548</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>647990</t>
+          <t>651656</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,71%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>513343</t>
+          <t>517429</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>596835</t>
+          <t>595747</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>33,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1097177</t>
+          <t>1108390</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1216126</t>
+          <t>1225464</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,98%</t>
         </is>
       </c>
     </row>
@@ -5504,12 +5504,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>731519</t>
+          <t>737303</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>818918</t>
+          <t>821632</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,56%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>488826</t>
+          <t>495815</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>569268</t>
+          <t>577746</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1250692</t>
+          <t>1242618</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1363010</t>
+          <t>1368575</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,83%</t>
         </is>
       </c>
     </row>
@@ -5734,12 +5734,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1968</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11905</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5749,12 +5749,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3018</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14254</t>
+          <t>14144</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6108</t>
+          <t>6178</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20154</t>
+          <t>20835</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -5847,12 +5847,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17338</t>
+          <t>19031</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5862,12 +5862,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5882,12 +5882,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6917</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>22693</t>
+          <t>22421</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>12754</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>33279</t>
+          <t>33039</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>44305</t>
+          <t>43190</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>77421</t>
+          <t>74123</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>51331</t>
+          <t>49954</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81874</t>
+          <t>81066</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101012</t>
+          <t>100264</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>145233</t>
+          <t>145987</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>60067</t>
+          <t>58502</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>95114</t>
+          <t>95206</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6108,12 +6108,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>51390</t>
+          <t>51422</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>85101</t>
+          <t>83853</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6123,12 +6123,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>120801</t>
+          <t>120375</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>169668</t>
+          <t>168964</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>133721</t>
+          <t>132652</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>178320</t>
+          <t>175931</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>132690</t>
+          <t>134807</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>175466</t>
+          <t>175670</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,35%</t>
+          <t>38,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>280479</t>
+          <t>277965</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>346187</t>
+          <t>340151</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,27%</t>
         </is>
       </c>
     </row>
@@ -6299,12 +6299,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>157880</t>
+          <t>156862</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>205295</t>
+          <t>201155</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6314,12 +6314,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>130196</t>
+          <t>131754</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>174267</t>
+          <t>174463</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>38,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>298873</t>
+          <t>301746</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>361003</t>
+          <t>361159</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6384,12 +6384,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,51%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>59969</t>
+          <t>60002</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>97897</t>
+          <t>98015</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>140273</t>
+          <t>138966</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>193250</t>
+          <t>190120</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>210228</t>
+          <t>208356</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>271762</t>
+          <t>272715</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>90372</t>
+          <t>90710</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>135516</t>
+          <t>134838</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>176581</t>
+          <t>174081</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>234759</t>
+          <t>233272</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>278815</t>
+          <t>279474</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>351386</t>
+          <t>357144</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>437453</t>
+          <t>440543</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>523276</t>
+          <t>529124</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>651200</t>
+          <t>648973</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>749987</t>
+          <t>750372</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1117944</t>
+          <t>1114007</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1245581</t>
+          <t>1240945</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,82%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>440318</t>
+          <t>436406</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>521942</t>
+          <t>523920</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>473504</t>
+          <t>477523</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>560422</t>
+          <t>561314</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>938060</t>
+          <t>937307</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1055432</t>
+          <t>1052910</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>997956</t>
+          <t>1000391</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1113813</t>
+          <t>1112179</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>992411</t>
+          <t>993692</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1108661</t>
+          <t>1107067</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2022168</t>
+          <t>2026071</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2182922</t>
+          <t>2182113</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,33%</t>
         </is>
       </c>
     </row>
@@ -7094,12 +7094,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1155998</t>
+          <t>1159998</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1278070</t>
+          <t>1275486</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7109,12 +7109,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>37,41%</t>
+          <t>37,33%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7129,12 +7129,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>863533</t>
+          <t>858266</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>973811</t>
+          <t>974222</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7164,12 +7164,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2056987</t>
+          <t>2048823</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2218471</t>
+          <t>2208801</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18250</t>
+          <t>18136</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37566</t>
+          <t>37605</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7570,7 +7570,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45621</t>
+          <t>44440</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76490</t>
+          <t>78843</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68434</t>
+          <t>68296</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106289</t>
+          <t>105072</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35545</t>
+          <t>36176</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63119</t>
+          <t>61677</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>100964</t>
+          <t>103635</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>146884</t>
+          <t>146848</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>148276</t>
+          <t>148289</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>199332</t>
+          <t>201909</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7758,7 +7758,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,56%</t>
         </is>
       </c>
     </row>
@@ -7781,12 +7781,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>147412</t>
+          <t>145557</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>192449</t>
+          <t>189446</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>225561</t>
+          <t>224568</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>284737</t>
+          <t>282556</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>388414</t>
+          <t>388020</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>459482</t>
+          <t>460668</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>26,39%</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>160405</t>
+          <t>160565</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>206722</t>
+          <t>209400</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>194912</t>
+          <t>199511</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>249809</t>
+          <t>255723</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>369955</t>
+          <t>374275</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>441240</t>
+          <t>445694</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,53%</t>
         </is>
       </c>
     </row>
@@ -8007,12 +8007,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>129092</t>
+          <t>130737</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174027</t>
+          <t>174731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8022,12 +8022,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8042,12 +8042,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>151786</t>
+          <t>148967</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>201196</t>
+          <t>201421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>291298</t>
+          <t>291156</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>359793</t>
+          <t>357073</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -8120,12 +8120,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>154266</t>
+          <t>153861</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>202555</t>
+          <t>202517</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8155,12 +8155,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>132468</t>
+          <t>131632</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>179856</t>
+          <t>182153</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8170,12 +8170,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>296667</t>
+          <t>298412</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>363539</t>
+          <t>365225</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -8350,12 +8350,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>15726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38137</t>
+          <t>37693</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>30719</t>
+          <t>30090</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>56667</t>
+          <t>57591</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>50629</t>
+          <t>52136</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84580</t>
+          <t>85566</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -8463,12 +8463,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36505</t>
+          <t>37185</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65280</t>
+          <t>67181</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>58423</t>
+          <t>57789</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>94454</t>
+          <t>94550</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>105027</t>
+          <t>104100</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>148284</t>
+          <t>151288</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -8576,12 +8576,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>172113</t>
+          <t>167594</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>223010</t>
+          <t>223785</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>224253</t>
+          <t>223626</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>285642</t>
+          <t>285554</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>411662</t>
+          <t>408100</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>494681</t>
+          <t>490954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,1%</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>345064</t>
+          <t>350416</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>418767</t>
+          <t>423629</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>325853</t>
+          <t>326300</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>398078</t>
+          <t>394486</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>693852</t>
+          <t>690573</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>794143</t>
+          <t>794908</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>585633</t>
+          <t>586914</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>671138</t>
+          <t>673539</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>548261</t>
+          <t>547595</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>630274</t>
+          <t>626956</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8852,12 +8852,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1150470</t>
+          <t>1160354</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1273052</t>
+          <t>1278113</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8887,12 +8887,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>28,35%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,49%</t>
         </is>
       </c>
     </row>
@@ -8915,12 +8915,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>744342</t>
+          <t>740952</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>833169</t>
+          <t>832215</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8930,12 +8930,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8950,12 +8950,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>622378</t>
+          <t>627086</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>704826</t>
+          <t>711210</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8985,12 +8985,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1395742</t>
+          <t>1395755</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1517653</t>
+          <t>1520361</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,46%</t>
         </is>
       </c>
     </row>
@@ -9145,12 +9145,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3942</t>
+          <t>4151</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>17246</t>
+          <t>17152</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9160,12 +9160,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9180,12 +9180,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2068</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13498</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9195,12 +9195,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7755</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>25090</t>
+          <t>24395</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -9258,12 +9258,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3257</t>
+          <t>3105</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14752</t>
+          <t>14759</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9273,7 +9273,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -9293,12 +9293,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>5493</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>21468</t>
+          <t>20888</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9308,12 +9308,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11225</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29022</t>
+          <t>29349</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>42322</t>
+          <t>42977</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>71031</t>
+          <t>72552</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54118</t>
+          <t>55213</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>85074</t>
+          <t>86394</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>103154</t>
+          <t>104161</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146133</t>
+          <t>147401</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>90140</t>
+          <t>90567</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>127775</t>
+          <t>127592</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>91315</t>
+          <t>92788</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>129100</t>
+          <t>132098</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9534,12 +9534,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>195748</t>
+          <t>191827</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>249908</t>
+          <t>249338</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,77%</t>
         </is>
       </c>
     </row>
@@ -9597,12 +9597,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>150066</t>
+          <t>151219</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>193879</t>
+          <t>194101</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,44%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,49%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9632,12 +9632,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>155609</t>
+          <t>153737</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>200335</t>
+          <t>198566</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9667,12 +9667,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>316064</t>
+          <t>318421</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>383230</t>
+          <t>380890</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,79%</t>
         </is>
       </c>
     </row>
@@ -9710,12 +9710,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>170325</t>
+          <t>169843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>218694</t>
+          <t>215723</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9725,12 +9725,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>154761</t>
+          <t>153590</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>199606</t>
+          <t>197819</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>338938</t>
+          <t>339602</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>403760</t>
+          <t>402668</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -9940,12 +9940,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45235</t>
+          <t>45868</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>78368</t>
+          <t>78933</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>89128</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>130274</t>
+          <t>131487</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9990,12 +9990,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>141256</t>
+          <t>141940</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>196549</t>
+          <t>195105</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>85015</t>
+          <t>84618</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>125200</t>
+          <t>125813</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>179459</t>
+          <t>181734</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>239533</t>
+          <t>241305</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>283091</t>
+          <t>278579</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>355876</t>
+          <t>353036</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10166,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>382526</t>
+          <t>382502</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>458206</t>
+          <t>459821</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>532133</t>
+          <t>529493</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>628167</t>
+          <t>623526</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10216,12 +10216,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>940669</t>
+          <t>942236</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1061209</t>
+          <t>1061022</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -10279,12 +10279,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>629647</t>
+          <t>627183</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>721101</t>
+          <t>719999</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>641993</t>
+          <t>645730</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>739274</t>
+          <t>740526</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1298925</t>
+          <t>1305740</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1441250</t>
+          <t>1441212</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>904021</t>
+          <t>905995</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1010910</t>
+          <t>1007164</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>884871</t>
+          <t>882030</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1000846</t>
+          <t>993111</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10442,12 +10442,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1823733</t>
+          <t>1826581</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1971937</t>
+          <t>1966534</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,5%</t>
         </is>
       </c>
     </row>
@@ -10505,12 +10505,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1100986</t>
+          <t>1097063</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1217088</t>
+          <t>1215453</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10520,12 +10520,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -10540,12 +10540,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>939468</t>
+          <t>942734</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1056858</t>
+          <t>1049116</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10555,12 +10555,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10575,12 +10575,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2075747</t>
+          <t>2085640</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2229062</t>
+          <t>2238731</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10590,12 +10590,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,45%</t>
         </is>
       </c>
     </row>
@@ -10961,32 +10961,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>21837</t>
+          <t>23954</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15077</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30653</t>
+          <t>34985</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10996,32 +10996,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>64982</t>
+          <t>68907</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54157</t>
+          <t>57568</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75658</t>
+          <t>80479</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11031,32 +11031,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>86819</t>
+          <t>92861</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75555</t>
+          <t>80302</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101125</t>
+          <t>107827</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -11074,32 +11074,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>46317</t>
+          <t>52911</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35897</t>
+          <t>41129</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>58512</t>
+          <t>67394</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11109,17 +11109,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>85232</t>
+          <t>92785</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73517</t>
+          <t>80316</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98887</t>
+          <t>108312</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11129,12 +11129,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11144,32 +11144,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>131549</t>
+          <t>145696</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>115289</t>
+          <t>128350</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148490</t>
+          <t>167712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,99%</t>
         </is>
       </c>
     </row>
@@ -11187,32 +11187,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>101248</t>
+          <t>106515</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87173</t>
+          <t>91275</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>117465</t>
+          <t>123763</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11222,32 +11222,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>182739</t>
+          <t>193486</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>164211</t>
+          <t>174324</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>203982</t>
+          <t>211912</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11257,32 +11257,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>283986</t>
+          <t>300001</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>259062</t>
+          <t>275119</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>308790</t>
+          <t>327417</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>23,41%</t>
         </is>
       </c>
     </row>
@@ -11300,32 +11300,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>106270</t>
+          <t>111226</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>89123</t>
+          <t>94139</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>124907</t>
+          <t>131997</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11335,32 +11335,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>147351</t>
+          <t>163025</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>131544</t>
+          <t>147005</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>164359</t>
+          <t>182034</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11370,32 +11370,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>253621</t>
+          <t>274251</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>229587</t>
+          <t>248828</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>278271</t>
+          <t>300904</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,52%</t>
         </is>
       </c>
     </row>
@@ -11413,32 +11413,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>114313</t>
+          <t>131113</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97657</t>
+          <t>113801</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>132958</t>
+          <t>152593</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,87%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11448,32 +11448,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>159887</t>
+          <t>174864</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>143223</t>
+          <t>158745</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>177200</t>
+          <t>193742</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11483,32 +11483,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>274199</t>
+          <t>305977</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>250416</t>
+          <t>277351</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>299757</t>
+          <t>334130</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,88%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -11526,32 +11526,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>123984</t>
+          <t>151822</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>105975</t>
+          <t>131050</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>141365</t>
+          <t>175746</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -11561,32 +11561,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>114288</t>
+          <t>127867</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>98337</t>
+          <t>112906</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>131596</t>
+          <t>146934</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11596,32 +11596,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>238273</t>
+          <t>279689</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>215159</t>
+          <t>254377</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>263526</t>
+          <t>313060</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>22,39%</t>
         </is>
       </c>
     </row>
@@ -11639,17 +11639,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>513969</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>513969</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>513969</t>
+          <t>577542</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11674,17 +11674,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>754478</t>
+          <t>820935</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>754478</t>
+          <t>820935</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>754478</t>
+          <t>820935</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11709,17 +11709,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1268447</t>
+          <t>1398476</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1268447</t>
+          <t>1398476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1268447</t>
+          <t>1398476</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11756,32 +11756,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>26543</t>
+          <t>29884</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15837</t>
+          <t>19984</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37453</t>
+          <t>40951</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11791,32 +11791,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>35565</t>
+          <t>37772</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>24651</t>
+          <t>27355</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52702</t>
+          <t>53164</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11826,32 +11826,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>62108</t>
+          <t>67656</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>45971</t>
+          <t>53902</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>81250</t>
+          <t>86268</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -11869,32 +11869,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>68405</t>
+          <t>77458</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45806</t>
+          <t>61181</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>89103</t>
+          <t>98982</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11904,32 +11904,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>90894</t>
+          <t>102082</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>67363</t>
+          <t>86176</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>113949</t>
+          <t>119637</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11939,32 +11939,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>159299</t>
+          <t>179539</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>128959</t>
+          <t>155133</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>191423</t>
+          <t>206268</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>3,52%</t>
         </is>
       </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,69%</t>
         </is>
       </c>
     </row>
@@ -11982,32 +11982,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>222450</t>
+          <t>240505</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>152543</t>
+          <t>210444</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>262701</t>
+          <t>271519</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12017,32 +12017,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>302868</t>
+          <t>341043</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>226274</t>
+          <t>315494</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>352816</t>
+          <t>372069</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12052,32 +12052,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>525318</t>
+          <t>581548</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>424182</t>
+          <t>538800</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>599843</t>
+          <t>625030</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>14,2%</t>
         </is>
       </c>
     </row>
@@ -12095,32 +12095,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>533818</t>
+          <t>323822</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>311600</t>
+          <t>289220</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1101965</t>
+          <t>360971</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12130,32 +12130,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>275455</t>
+          <t>308811</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>205219</t>
+          <t>281877</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>321367</t>
+          <t>341022</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12165,32 +12165,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>809273</t>
+          <t>632633</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>574181</t>
+          <t>588348</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1408238</t>
+          <t>681195</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -12208,32 +12208,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>578908</t>
+          <t>623192</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>407725</t>
+          <t>576590</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>669578</t>
+          <t>677004</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12243,32 +12243,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>807409</t>
+          <t>598721</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>615116</t>
+          <t>562837</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1162593</t>
+          <t>637558</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12278,32 +12278,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1386318</t>
+          <t>1221913</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1165198</t>
+          <t>1160758</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1853362</t>
+          <t>1285534</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>29,21%</t>
         </is>
       </c>
     </row>
@@ -12321,32 +12321,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>860203</t>
+          <t>935707</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>588695</t>
+          <t>879572</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>984543</t>
+          <t>991343</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>39,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12356,32 +12356,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>724632</t>
+          <t>781929</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>558305</t>
+          <t>738561</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>831355</t>
+          <t>824685</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>36,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12391,32 +12391,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1584835</t>
+          <t>1717635</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1271818</t>
+          <t>1653525</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1774196</t>
+          <t>1790897</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>35,01%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>40,69%</t>
         </is>
       </c>
     </row>
@@ -12434,17 +12434,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12469,17 +12469,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2236824</t>
+          <t>2170358</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2236824</t>
+          <t>2170358</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2236824</t>
+          <t>2170358</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12504,17 +12504,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4527151</t>
+          <t>4400924</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4527151</t>
+          <t>4400924</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4527151</t>
+          <t>4400924</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12551,32 +12551,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4910</t>
+          <t>5232</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14917</t>
+          <t>14118</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12586,17 +12586,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5654</t>
+          <t>6314</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2542</t>
+          <t>3128</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12606,12 +12606,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12621,32 +12621,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>10564</t>
+          <t>11545</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5673</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20430</t>
+          <t>20195</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -12664,32 +12664,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>30299</t>
+          <t>35085</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20214</t>
+          <t>24112</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>44132</t>
+          <t>51923</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12699,32 +12699,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>27400</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12096</t>
+          <t>18234</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26599</t>
+          <t>38806</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12734,32 +12734,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>48440</t>
+          <t>62485</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37572</t>
+          <t>48829</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>64734</t>
+          <t>84108</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -12777,32 +12777,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>75075</t>
+          <t>82481</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60199</t>
+          <t>66901</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93042</t>
+          <t>100819</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12812,32 +12812,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>105891</t>
+          <t>118707</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>88714</t>
+          <t>102911</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>122042</t>
+          <t>137111</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12847,32 +12847,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>180966</t>
+          <t>201188</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>157491</t>
+          <t>177839</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>204395</t>
+          <t>227374</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -12890,32 +12890,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>93784</t>
+          <t>102939</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76385</t>
+          <t>86289</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>112593</t>
+          <t>122378</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12925,32 +12925,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>111931</t>
+          <t>127838</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>97408</t>
+          <t>111032</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>130072</t>
+          <t>146364</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12960,32 +12960,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>205715</t>
+          <t>230777</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>180874</t>
+          <t>206835</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>228785</t>
+          <t>257732</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -13003,32 +13003,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>180640</t>
+          <t>205527</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>159042</t>
+          <t>180268</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>207628</t>
+          <t>232325</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13038,32 +13038,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>206832</t>
+          <t>221379</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>185979</t>
+          <t>198256</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>226502</t>
+          <t>243540</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>31,39%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13073,32 +13073,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>387472</t>
+          <t>426906</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>357406</t>
+          <t>392660</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>420549</t>
+          <t>461073</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,54%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,91%</t>
         </is>
       </c>
     </row>
@@ -13116,32 +13116,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>261915</t>
+          <t>280323</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>236869</t>
+          <t>250129</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>291442</t>
+          <t>311566</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13151,32 +13151,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>210431</t>
+          <t>231742</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>190302</t>
+          <t>210629</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>234181</t>
+          <t>255828</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>31,6%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>35,54%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13186,32 +13186,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>472346</t>
+          <t>512065</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>438449</t>
+          <t>478039</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>511871</t>
+          <t>551245</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>38,15%</t>
         </is>
       </c>
     </row>
@@ -13229,17 +13229,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13264,17 +13264,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>658880</t>
+          <t>733380</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>658880</t>
+          <t>733380</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>658880</t>
+          <t>733380</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13299,17 +13299,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1305503</t>
+          <t>1444967</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1305503</t>
+          <t>1444967</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1305503</t>
+          <t>1444967</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13346,32 +13346,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>53290</t>
+          <t>59069</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40479</t>
+          <t>46343</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69383</t>
+          <t>75051</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13381,67 +13381,67 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>106201</t>
+          <t>112993</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>86775</t>
+          <t>97439</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>126384</t>
+          <t>133400</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>172062</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>151806</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>199057</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
           <t>2,38%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>159490</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>132946</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>184782</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,75%</t>
         </is>
       </c>
     </row>
@@ -13459,32 +13459,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>145021</t>
+          <t>165454</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>109052</t>
+          <t>143009</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>171459</t>
+          <t>193592</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13494,32 +13494,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>194267</t>
+          <t>222266</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>157640</t>
+          <t>199598</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>222773</t>
+          <t>247041</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13529,32 +13529,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>339288</t>
+          <t>387721</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>291438</t>
+          <t>353570</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>379865</t>
+          <t>423798</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -13572,32 +13572,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>398772</t>
+          <t>429501</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>309483</t>
+          <t>391957</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>449980</t>
+          <t>469223</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13607,32 +13607,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>591498</t>
+          <t>653236</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>471503</t>
+          <t>611415</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>649031</t>
+          <t>692413</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13642,32 +13642,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>990270</t>
+          <t>1082738</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>848543</t>
+          <t>1029509</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1071427</t>
+          <t>1135968</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,68%</t>
         </is>
       </c>
     </row>
@@ -13685,32 +13685,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>733873</t>
+          <t>537987</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>511137</t>
+          <t>494127</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1327150</t>
+          <t>580932</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13720,32 +13720,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>534737</t>
+          <t>599674</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>443861</t>
+          <t>559777</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>590690</t>
+          <t>642098</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13755,32 +13755,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1268610</t>
+          <t>1137661</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1027232</t>
+          <t>1078231</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2025024</t>
+          <t>1200785</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -13798,32 +13798,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>873861</t>
+          <t>959832</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>701212</t>
+          <t>904951</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>964993</t>
+          <t>1017605</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>28,91%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13833,32 +13833,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1174128</t>
+          <t>994964</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>981464</t>
+          <t>948716</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1642775</t>
+          <t>1042029</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>25,47%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>27,98%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13868,32 +13868,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2047989</t>
+          <t>1954796</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1814856</t>
+          <t>1881637</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2579478</t>
+          <t>2025911</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -13911,32 +13911,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1246103</t>
+          <t>1367852</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>956404</t>
+          <t>1295561</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1363972</t>
+          <t>1431441</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13946,32 +13946,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1049352</t>
+          <t>1141539</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>850195</t>
+          <t>1090751</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1147983</t>
+          <t>1192148</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>28,75%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>29,28%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13981,32 +13981,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2295455</t>
+          <t>2509390</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2003700</t>
+          <t>2419306</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2467481</t>
+          <t>2593757</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -14024,17 +14024,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3450920</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3450920</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3450920</t>
+          <t>3519695</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14059,17 +14059,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3650182</t>
+          <t>3724673</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3650182</t>
+          <t>3724673</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3650182</t>
+          <t>3724673</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14094,17 +14094,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>7101102</t>
+          <t>7244368</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>7101102</t>
+          <t>7244368</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>7101102</t>
+          <t>7244368</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
